--- a/SOC 2 Security Readiness & Audit Evidence Package for Live E-commerce Platform/01_Control_Matrix/SOC2_Control_Matrix.xlsx
+++ b/SOC 2 Security Readiness & Audit Evidence Package for Live E-commerce Platform/01_Control_Matrix/SOC2_Control_Matrix.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="241" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEFF4E71-022F-40DF-A75C-E194EA4EE8F3}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F79DF87E-515F-4C15-BD88-28D052FB131A}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="182">
   <si>
     <t>Control ID</t>
   </si>
@@ -69,6 +69,15 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Test of Design (ToD)</t>
+  </si>
+  <si>
+    <t>Test of Operating Effectiveness (ToOE)</t>
+  </si>
+  <si>
+    <t>Testing Result</t>
+  </si>
+  <si>
     <t>C-01</t>
   </si>
   <si>
@@ -105,6 +114,15 @@
     <t>Not Implemented</t>
   </si>
   <si>
+    <t xml:space="preserve"> Fail</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Ineffective</t>
+  </si>
+  <si>
     <t>C-02</t>
   </si>
   <si>
@@ -132,6 +150,9 @@
     <t>Code inspection showing absence of RBAC</t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
     <t>C-03</t>
   </si>
   <si>
@@ -184,6 +205,12 @@
   </si>
   <si>
     <t>Partially Implemented</t>
+  </si>
+  <si>
+    <t>Partial</t>
+  </si>
+  <si>
+    <t>Needs Improvement</t>
   </si>
   <si>
     <t>C-05</t>
@@ -556,7 +583,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,6 +602,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFED7D31"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -599,13 +633,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -920,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -929,9 +964,12 @@
     <col min="4" max="9" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1">
+    <row r="1" spans="1:15" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -968,689 +1006,860 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" ht="60.75">
+    <row r="2" spans="1:15" ht="60.75">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="45.75">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>39</v>
+      </c>
+      <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="45.75">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="30.75">
+      <c r="A5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="30.75">
+      <c r="A6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N6" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="30.75">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s">
+        <v>75</v>
+      </c>
+      <c r="J7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="30.75">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" t="s">
+        <v>58</v>
+      </c>
+      <c r="O8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="30.75">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="30.75">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" t="s">
-        <v>23</v>
+      <c r="D10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H10" t="s">
+        <v>100</v>
+      </c>
+      <c r="I10" t="s">
+        <v>101</v>
+      </c>
+      <c r="J10" t="s">
+        <v>94</v>
+      </c>
+      <c r="K10" t="s">
+        <v>102</v>
+      </c>
+      <c r="L10" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="45.75">
-      <c r="A3" t="s">
+    <row r="11" spans="1:15" ht="30.75">
+      <c r="A11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J11" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="K11" t="s">
+        <v>102</v>
+      </c>
+      <c r="L11" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" t="s">
+        <v>28</v>
+      </c>
+      <c r="O11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="60.75">
+      <c r="A12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G12" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="J12" t="s">
+        <v>94</v>
+      </c>
+      <c r="K12" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="L12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="M12" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="N12" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="O12" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="4" spans="1:12" ht="45.75">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="2" t="s">
+    <row r="13" spans="1:15" ht="45.75">
+      <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G13" t="s">
+        <v>127</v>
+      </c>
+      <c r="H13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" t="s">
         <v>39</v>
       </c>
-      <c r="I4" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
+      <c r="N13" t="s">
+        <v>28</v>
+      </c>
+      <c r="O13" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="30.75">
-      <c r="A5" t="s">
+    <row r="14" spans="1:15" ht="30.75">
+      <c r="A14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" t="s">
+        <v>135</v>
+      </c>
+      <c r="G14" t="s">
+        <v>136</v>
+      </c>
+      <c r="H14" t="s">
+        <v>137</v>
+      </c>
+      <c r="I14" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" t="s">
+        <v>39</v>
+      </c>
+      <c r="N14" t="s">
+        <v>28</v>
+      </c>
+      <c r="O14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="45.75">
+      <c r="A15" t="s">
+        <v>139</v>
+      </c>
+      <c r="B15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C15" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F15" t="s">
+        <v>144</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H15" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" t="s">
+        <v>147</v>
+      </c>
+      <c r="J15" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" t="s">
+        <v>58</v>
+      </c>
+      <c r="O15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="30.75">
+      <c r="A16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" t="s">
+        <v>150</v>
+      </c>
+      <c r="D16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" t="s">
+        <v>153</v>
+      </c>
+      <c r="G16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H16" t="s">
+        <v>155</v>
+      </c>
+      <c r="I16" t="s">
+        <v>156</v>
+      </c>
+      <c r="J16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K16" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" t="s">
+        <v>39</v>
+      </c>
+      <c r="N16" t="s">
+        <v>28</v>
+      </c>
+      <c r="O16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="30.75">
+      <c r="A17" t="s">
+        <v>157</v>
+      </c>
+      <c r="B17" t="s">
         <v>41</v>
       </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" t="s">
-        <v>22</v>
-      </c>
-      <c r="L5" t="s">
-        <v>50</v>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>158</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F17" t="s">
+        <v>160</v>
+      </c>
+      <c r="G17" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17" t="s">
+        <v>163</v>
+      </c>
+      <c r="J17" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17" t="s">
+        <v>102</v>
+      </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" t="s">
+        <v>39</v>
+      </c>
+      <c r="N17" t="s">
+        <v>28</v>
+      </c>
+      <c r="O17" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="30.75">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" t="s">
-        <v>21</v>
-      </c>
-      <c r="K6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L6" t="s">
-        <v>23</v>
+    <row r="18" spans="1:15" ht="30.75">
+      <c r="A18" t="s">
+        <v>164</v>
+      </c>
+      <c r="B18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" t="s">
+        <v>166</v>
+      </c>
+      <c r="D18" t="s">
+        <v>167</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F18" t="s">
+        <v>169</v>
+      </c>
+      <c r="G18" t="s">
+        <v>170</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I18" t="s">
+        <v>172</v>
+      </c>
+      <c r="J18" t="s">
+        <v>94</v>
+      </c>
+      <c r="K18" t="s">
+        <v>173</v>
+      </c>
+      <c r="L18" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" t="s">
+        <v>39</v>
+      </c>
+      <c r="N18" t="s">
+        <v>28</v>
+      </c>
+      <c r="O18" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="30.75">
-      <c r="A7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F7" t="s">
-        <v>63</v>
-      </c>
-      <c r="G7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H7" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="30.75">
-      <c r="A8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" t="s">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="30.75">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="30.75">
-      <c r="A10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" t="s">
-        <v>89</v>
-      </c>
-      <c r="G10" t="s">
-        <v>90</v>
-      </c>
-      <c r="H10" t="s">
-        <v>91</v>
-      </c>
-      <c r="I10" t="s">
-        <v>92</v>
-      </c>
-      <c r="J10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" t="s">
-        <v>93</v>
-      </c>
-      <c r="L10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="30.75">
-      <c r="A11" t="s">
+    <row r="19" spans="1:15" ht="30.75">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+      <c r="B19" t="s">
+        <v>175</v>
+      </c>
+      <c r="C19" t="s">
+        <v>166</v>
+      </c>
+      <c r="D19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G19" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" t="s">
+        <v>180</v>
+      </c>
+      <c r="I19" t="s">
+        <v>181</v>
+      </c>
+      <c r="J19" t="s">
         <v>94</v>
       </c>
-      <c r="B11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" t="s">
-        <v>96</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" t="s">
-        <v>99</v>
-      </c>
-      <c r="G11" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="K19" t="s">
         <v>102</v>
       </c>
-      <c r="J11" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" t="s">
-        <v>93</v>
-      </c>
-      <c r="L11" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="60.75">
-      <c r="A12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B12" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" t="s">
-        <v>106</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="J12" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="45.75">
-      <c r="A13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F13" t="s">
-        <v>117</v>
-      </c>
-      <c r="G13" t="s">
-        <v>118</v>
-      </c>
-      <c r="H13" t="s">
-        <v>119</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J13" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="30.75">
-      <c r="A14" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" t="s">
-        <v>124</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F14" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" t="s">
-        <v>127</v>
-      </c>
-      <c r="H14" t="s">
-        <v>128</v>
-      </c>
-      <c r="I14" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" t="s">
-        <v>93</v>
-      </c>
-      <c r="L14" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="45.75">
-      <c r="A15" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C15" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F15" t="s">
-        <v>135</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H15" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" t="s">
-        <v>138</v>
-      </c>
-      <c r="J15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s">
-        <v>22</v>
-      </c>
-      <c r="L15" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="30.75">
-      <c r="A16" t="s">
-        <v>139</v>
-      </c>
-      <c r="B16" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" t="s">
-        <v>141</v>
-      </c>
-      <c r="D16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F16" t="s">
-        <v>144</v>
-      </c>
-      <c r="G16" t="s">
-        <v>145</v>
-      </c>
-      <c r="H16" t="s">
-        <v>146</v>
-      </c>
-      <c r="I16" t="s">
-        <v>147</v>
-      </c>
-      <c r="J16" t="s">
-        <v>85</v>
-      </c>
-      <c r="K16" t="s">
-        <v>93</v>
-      </c>
-      <c r="L16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="30.75">
-      <c r="A17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F17" t="s">
-        <v>151</v>
-      </c>
-      <c r="G17" t="s">
-        <v>152</v>
-      </c>
-      <c r="H17" t="s">
-        <v>153</v>
-      </c>
-      <c r="I17" t="s">
-        <v>154</v>
-      </c>
-      <c r="J17" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" t="s">
-        <v>93</v>
-      </c>
-      <c r="L17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="30.75">
-      <c r="A18" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" t="s">
-        <v>156</v>
-      </c>
-      <c r="C18" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" t="s">
-        <v>158</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G18" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I18" t="s">
-        <v>163</v>
-      </c>
-      <c r="J18" t="s">
-        <v>85</v>
-      </c>
-      <c r="K18" t="s">
-        <v>164</v>
-      </c>
-      <c r="L18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="30.75">
-      <c r="A19" t="s">
-        <v>165</v>
-      </c>
-      <c r="B19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C19" t="s">
-        <v>157</v>
-      </c>
-      <c r="D19" t="s">
-        <v>167</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F19" t="s">
-        <v>169</v>
-      </c>
-      <c r="G19" t="s">
-        <v>170</v>
-      </c>
-      <c r="H19" t="s">
-        <v>171</v>
-      </c>
-      <c r="I19" t="s">
-        <v>172</v>
-      </c>
-      <c r="J19" t="s">
-        <v>85</v>
-      </c>
-      <c r="K19" t="s">
-        <v>93</v>
-      </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>26</v>
+      </c>
+      <c r="M19" t="s">
+        <v>39</v>
+      </c>
+      <c r="N19" t="s">
+        <v>28</v>
+      </c>
+      <c r="O19" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/SOC 2 Security Readiness & Audit Evidence Package for Live E-commerce Platform/01_Control_Matrix/SOC2_Control_Matrix.xlsx
+++ b/SOC 2 Security Readiness & Audit Evidence Package for Live E-commerce Platform/01_Control_Matrix/SOC2_Control_Matrix.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="302" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F79DF87E-515F-4C15-BD88-28D052FB131A}"/>
+  <xr:revisionPtr revIDLastSave="341" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A8BD179-FA46-49FC-A8B0-65EC3EEB0C24}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="185">
   <si>
     <t>Control ID</t>
   </si>
@@ -78,6 +78,12 @@
     <t>Testing Result</t>
   </si>
   <si>
+    <t>Control Effectiveness</t>
+  </si>
+  <si>
+    <t>Residual Risk</t>
+  </si>
+  <si>
     <t>C-01</t>
   </si>
   <si>
@@ -213,6 +219,12 @@
     <t>Needs Improvement</t>
   </si>
   <si>
+    <t>Partially Effective</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
     <t>C-05</t>
   </si>
   <si>
@@ -337,9 +349,6 @@
   </si>
   <si>
     <t>No review records</t>
-  </si>
-  <si>
-    <t>Medium</t>
   </si>
   <si>
     <t>C-10</t>
@@ -955,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -967,9 +976,11 @@
     <col min="13" max="13" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="35" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1">
+    <row r="1" spans="1:17" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1015,851 +1026,965 @@
       <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" ht="60.75">
+    <row r="2" spans="1:17" ht="60.75">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="45.75">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="45.75">
+      <c r="A4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="30.75">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="30.75">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" t="s">
+        <v>70</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+      <c r="O6" t="s">
+        <v>61</v>
+      </c>
+      <c r="P6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="30.75">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="30.75">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" t="s">
+        <v>60</v>
+      </c>
+      <c r="N8" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" t="s">
+        <v>61</v>
+      </c>
+      <c r="P8" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="30.75">
+      <c r="A9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J9" t="s">
+        <v>98</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="30.75">
+      <c r="A10" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="D10" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="30.75">
+      <c r="A11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" t="s">
         <v>26</v>
       </c>
-      <c r="M2" t="s">
+      <c r="K11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" t="s">
+        <v>31</v>
+      </c>
+      <c r="P11" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="60.75">
+      <c r="A12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" t="s">
+        <v>121</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J12" t="s">
+        <v>98</v>
+      </c>
+      <c r="K12" t="s">
         <v>27</v>
       </c>
-      <c r="N2" t="s">
+      <c r="L12" t="s">
         <v>28</v>
       </c>
-      <c r="O2" t="s">
+      <c r="M12" t="s">
         <v>29</v>
       </c>
+      <c r="N12" t="s">
+        <v>30</v>
+      </c>
+      <c r="O12" t="s">
+        <v>31</v>
+      </c>
+      <c r="P12" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" ht="45.75">
-      <c r="A3" t="s">
+    <row r="13" spans="1:17" ht="45.75">
+      <c r="A13" t="s">
+        <v>124</v>
+      </c>
+      <c r="B13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" t="s">
+        <v>28</v>
+      </c>
+      <c r="M13" t="s">
+        <v>41</v>
+      </c>
+      <c r="N13" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="O13" t="s">
+        <v>31</v>
+      </c>
+      <c r="P13" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="30.75">
+      <c r="A14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F14" t="s">
+        <v>138</v>
+      </c>
+      <c r="G14" t="s">
+        <v>139</v>
+      </c>
+      <c r="H14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I14" t="s">
+        <v>141</v>
+      </c>
+      <c r="J14" t="s">
         <v>26</v>
       </c>
-      <c r="M3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="K14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" t="s">
         <v>28</v>
       </c>
-      <c r="O3" t="s">
-        <v>29</v>
+      <c r="M14" t="s">
+        <v>41</v>
+      </c>
+      <c r="N14" t="s">
+        <v>30</v>
+      </c>
+      <c r="O14" t="s">
+        <v>31</v>
+      </c>
+      <c r="P14" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="45.75">
-      <c r="A4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="15" spans="1:17" ht="45.75">
+      <c r="A15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F15" t="s">
+        <v>147</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H15" t="s">
+        <v>149</v>
+      </c>
+      <c r="I15" t="s">
+        <v>150</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" t="s">
+        <v>27</v>
+      </c>
+      <c r="L15" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" t="s">
+        <v>60</v>
+      </c>
+      <c r="O15" t="s">
+        <v>61</v>
+      </c>
+      <c r="P15" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="30.75">
+      <c r="A16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" t="s">
+        <v>154</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F16" t="s">
+        <v>156</v>
+      </c>
+      <c r="G16" t="s">
+        <v>157</v>
+      </c>
+      <c r="H16" t="s">
+        <v>158</v>
+      </c>
+      <c r="I16" t="s">
+        <v>159</v>
+      </c>
+      <c r="J16" t="s">
+        <v>98</v>
+      </c>
+      <c r="K16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L16" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" t="s">
         <v>41</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="N16" t="s">
+        <v>30</v>
+      </c>
+      <c r="O16" t="s">
+        <v>31</v>
+      </c>
+      <c r="P16" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="30.75">
+      <c r="A17" t="s">
+        <v>160</v>
+      </c>
+      <c r="B17" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>161</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" t="s">
+        <v>164</v>
+      </c>
+      <c r="H17" t="s">
+        <v>165</v>
+      </c>
+      <c r="I17" t="s">
+        <v>166</v>
+      </c>
+      <c r="J17" t="s">
+        <v>98</v>
+      </c>
+      <c r="K17" t="s">
+        <v>63</v>
+      </c>
+      <c r="L17" t="s">
         <v>28</v>
       </c>
-      <c r="O4" t="s">
-        <v>29</v>
+      <c r="M17" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O17" t="s">
+        <v>31</v>
+      </c>
+      <c r="P17" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="30.75">
-      <c r="A5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>57</v>
-      </c>
-      <c r="M5" t="s">
-        <v>58</v>
-      </c>
-      <c r="N5" t="s">
-        <v>58</v>
-      </c>
-      <c r="O5" t="s">
-        <v>59</v>
+    <row r="18" spans="1:17" ht="30.75">
+      <c r="A18" t="s">
+        <v>167</v>
+      </c>
+      <c r="B18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F18" t="s">
+        <v>172</v>
+      </c>
+      <c r="G18" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I18" t="s">
+        <v>175</v>
+      </c>
+      <c r="J18" t="s">
+        <v>98</v>
+      </c>
+      <c r="K18" t="s">
+        <v>176</v>
+      </c>
+      <c r="L18" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" t="s">
+        <v>41</v>
+      </c>
+      <c r="N18" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" t="s">
+        <v>31</v>
+      </c>
+      <c r="P18" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="30.75">
-      <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="2" t="s">
+    <row r="19" spans="1:17" ht="30.75">
+      <c r="A19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" t="s">
+        <v>179</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G19" t="s">
+        <v>182</v>
+      </c>
+      <c r="H19" t="s">
+        <v>183</v>
+      </c>
+      <c r="I19" t="s">
+        <v>184</v>
+      </c>
+      <c r="J19" t="s">
+        <v>98</v>
+      </c>
+      <c r="K19" t="s">
         <v>63</v>
       </c>
-      <c r="G6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N6" t="s">
-        <v>58</v>
-      </c>
-      <c r="O6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="30.75">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="L19" t="s">
         <v>28</v>
       </c>
-      <c r="O7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="30.75">
-      <c r="A8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" t="s">
-        <v>84</v>
-      </c>
-      <c r="J8" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" t="s">
-        <v>57</v>
-      </c>
-      <c r="M8" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" t="s">
-        <v>58</v>
-      </c>
-      <c r="O8" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="30.75">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F9" t="s">
-        <v>90</v>
-      </c>
-      <c r="G9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J9" t="s">
-        <v>94</v>
-      </c>
-      <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="30.75">
-      <c r="A10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="M19" t="s">
         <v>41</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F10" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" t="s">
-        <v>99</v>
-      </c>
-      <c r="H10" t="s">
-        <v>100</v>
-      </c>
-      <c r="I10" t="s">
-        <v>101</v>
-      </c>
-      <c r="J10" t="s">
-        <v>94</v>
-      </c>
-      <c r="K10" t="s">
-        <v>102</v>
-      </c>
-      <c r="L10" t="s">
-        <v>26</v>
-      </c>
-      <c r="M10" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="30.75">
-      <c r="A11" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C11" t="s">
-        <v>105</v>
-      </c>
-      <c r="D11" t="s">
-        <v>106</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G11" t="s">
-        <v>109</v>
-      </c>
-      <c r="H11" t="s">
-        <v>110</v>
-      </c>
-      <c r="I11" t="s">
-        <v>111</v>
-      </c>
-      <c r="J11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K11" t="s">
-        <v>102</v>
-      </c>
-      <c r="L11" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" t="s">
-        <v>28</v>
-      </c>
-      <c r="O11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="60.75">
-      <c r="A12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G12" t="s">
-        <v>118</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" t="s">
-        <v>94</v>
-      </c>
-      <c r="K12" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" t="s">
-        <v>26</v>
-      </c>
-      <c r="M12" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" t="s">
-        <v>28</v>
-      </c>
-      <c r="O12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="45.75">
-      <c r="A13" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F13" t="s">
-        <v>126</v>
-      </c>
-      <c r="G13" t="s">
-        <v>127</v>
-      </c>
-      <c r="H13" t="s">
-        <v>128</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="J13" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" t="s">
-        <v>26</v>
-      </c>
-      <c r="M13" t="s">
-        <v>39</v>
-      </c>
-      <c r="N13" t="s">
-        <v>28</v>
-      </c>
-      <c r="O13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="30.75">
-      <c r="A14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" t="s">
-        <v>135</v>
-      </c>
-      <c r="G14" t="s">
-        <v>136</v>
-      </c>
-      <c r="H14" t="s">
-        <v>137</v>
-      </c>
-      <c r="I14" t="s">
-        <v>138</v>
-      </c>
-      <c r="J14" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L14" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" t="s">
-        <v>39</v>
-      </c>
-      <c r="N14" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="45.75">
-      <c r="A15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" t="s">
-        <v>144</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H15" t="s">
-        <v>146</v>
-      </c>
-      <c r="I15" t="s">
-        <v>147</v>
-      </c>
-      <c r="J15" t="s">
-        <v>24</v>
-      </c>
-      <c r="K15" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" t="s">
-        <v>57</v>
-      </c>
-      <c r="M15" t="s">
-        <v>58</v>
-      </c>
-      <c r="N15" t="s">
-        <v>58</v>
-      </c>
-      <c r="O15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="30.75">
-      <c r="A16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" t="s">
-        <v>149</v>
-      </c>
-      <c r="C16" t="s">
-        <v>150</v>
-      </c>
-      <c r="D16" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F16" t="s">
-        <v>153</v>
-      </c>
-      <c r="G16" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" t="s">
-        <v>155</v>
-      </c>
-      <c r="I16" t="s">
-        <v>156</v>
-      </c>
-      <c r="J16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K16" t="s">
-        <v>102</v>
-      </c>
-      <c r="L16" t="s">
-        <v>26</v>
-      </c>
-      <c r="M16" t="s">
-        <v>39</v>
-      </c>
-      <c r="N16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="30.75">
-      <c r="A17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F17" t="s">
-        <v>160</v>
-      </c>
-      <c r="G17" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" t="s">
-        <v>162</v>
-      </c>
-      <c r="I17" t="s">
-        <v>163</v>
-      </c>
-      <c r="J17" t="s">
-        <v>94</v>
-      </c>
-      <c r="K17" t="s">
-        <v>102</v>
-      </c>
-      <c r="L17" t="s">
-        <v>26</v>
-      </c>
-      <c r="M17" t="s">
-        <v>39</v>
-      </c>
-      <c r="N17" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="30.75">
-      <c r="A18" t="s">
-        <v>164</v>
-      </c>
-      <c r="B18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" t="s">
-        <v>166</v>
-      </c>
-      <c r="D18" t="s">
-        <v>167</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F18" t="s">
-        <v>169</v>
-      </c>
-      <c r="G18" t="s">
-        <v>170</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I18" t="s">
-        <v>172</v>
-      </c>
-      <c r="J18" t="s">
-        <v>94</v>
-      </c>
-      <c r="K18" t="s">
-        <v>173</v>
-      </c>
-      <c r="L18" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" t="s">
-        <v>39</v>
-      </c>
-      <c r="N18" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="30.75">
-      <c r="A19" t="s">
-        <v>174</v>
-      </c>
-      <c r="B19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D19" t="s">
-        <v>176</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F19" t="s">
-        <v>178</v>
-      </c>
-      <c r="G19" t="s">
-        <v>179</v>
-      </c>
-      <c r="H19" t="s">
-        <v>180</v>
-      </c>
-      <c r="I19" t="s">
-        <v>181</v>
-      </c>
-      <c r="J19" t="s">
-        <v>94</v>
-      </c>
-      <c r="K19" t="s">
-        <v>102</v>
-      </c>
-      <c r="L19" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" t="s">
-        <v>39</v>
-      </c>
       <c r="N19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O19" t="s">
-        <v>29</v>
+        <v>31</v>
+      </c>
+      <c r="P19" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
